--- a/insumos-piezas.xlsx
+++ b/insumos-piezas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
   <si>
     <t>ESPESOR</t>
   </si>
@@ -29,13 +29,88 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>CHAN-0.7-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAN-0.9-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAN-1.2-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAG-1.2-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAG-1.6-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAN-1.6-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAG-0.9-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAG-2.5-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAN-2.5-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAN-3.2-1.50x3.00</t>
+  </si>
+  <si>
+    <t>CHAN-4.7-1.50x3.00</t>
+  </si>
+  <si>
+    <t>CHAN-6.3-1.50x3.00</t>
+  </si>
+  <si>
+    <t>CHAN-9.5-1.50x3.00</t>
+  </si>
+  <si>
+    <t>CHAN-2.1-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAG-2.1-1.22x2.44</t>
+  </si>
+  <si>
+    <t>CHAI-0.7-1.00x2.00</t>
+  </si>
+  <si>
+    <t>CHAI-0.5-1.00x2.00</t>
+  </si>
+  <si>
+    <t>CHAI-1.0-1.25x2.50</t>
+  </si>
+  <si>
+    <t>CHAI-1.5-1.25x2.50</t>
+  </si>
+  <si>
+    <t>CHAI-2.0-1.25x2.50</t>
+  </si>
+  <si>
+    <t>CHAG-0.7-1.22x3.00</t>
+  </si>
+  <si>
+    <t>CHAA-0.4-1.00x2.00</t>
+  </si>
+  <si>
+    <t>CHAA-2.0-1.00x2.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,6 +129,34 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4A4F59"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,33 +183,38 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -400,92 +508,297 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>1.6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4">
-        <v>10013</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>1.6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4">
-        <v>20013</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2.14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4">
-        <v>10013</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
-        <v>20013</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4">
-        <v>10013</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="C16" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="B17" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4">
-        <v>20013</v>
+      <c r="C17" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>